--- a/src/attributions/attributions_ig_traj_142.xlsx
+++ b/src/attributions/attributions_ig_traj_142.xlsx
@@ -2140,34 +2140,34 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01193306543758196</v>
+        <v>0.02108714035380592</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0007477664179401485</v>
+        <v>0.008543617465844519</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.72054455835572e-11</v>
+        <v>-4.543769307836893e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01769385971135757</v>
+        <v>-0.08117717018539186</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,64 +2176,64 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006571857905320517</v>
+        <v>-0.026689950054601</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03133959476396701</v>
+        <v>0.06406624698789844</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>8.506860273564337e-05</v>
+        <v>0.00696664692997798</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00226611160423052</v>
+        <v>0.01935542587203351</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003777740554293905</v>
+        <v>0.009190521463527668</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.00075439570425524</v>
+        <v>-0.03223841531119074</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01936003124540913</v>
+        <v>-0.04412777045301946</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.001034775294646681</v>
+        <v>-0.03141071529156726</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,13 +2242,13 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.007265686115500927</v>
+        <v>0.009079695194128011</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.005553037571058925</v>
+        <v>-0.04188294315389707</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.007385575738722902</v>
+        <v>-0.04352932627630943</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0311500186614402</v>
+        <v>0.1885974300440999</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.001643539114268198</v>
+        <v>-0.01787285006101839</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.01904685341170872</v>
+        <v>-0.03680121429531766</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.001673224738120238</v>
+        <v>0.00299364400408125</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002541226292039973</v>
+        <v>0.00379527207467924</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01021669676635937</v>
+        <v>0.03235286019930583</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.008632258528764619</v>
+        <v>0.03365814599855989</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004009194334087429</v>
+        <v>0.0775502095062907</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.009962784442678171</v>
+        <v>0.06890372545381315</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02007406965515611</v>
+        <v>0.04830777519555056</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.004022475865872143</v>
+        <v>-0.04036955771185607</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.005633341795705944</v>
+        <v>-0.07688867257321355</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2380,10 +2380,10 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.004821437616875973</v>
+        <v>-0.02818499339242479</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,25 +2392,25 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.004390832042974894</v>
+        <v>-0.0177240167430984</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01671909765420796</v>
+        <v>0.04693849508879952</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.003500884822861545</v>
+        <v>-0.03806729450864015</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.005997282702391365</v>
+        <v>0.05181285269725404</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.002201313277367509</v>
+        <v>0.04976238249093222</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.004406253196866083</v>
+        <v>-0.03104953094840956</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,13 +2446,13 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003590184738508282</v>
+        <v>-0.02704992275589803</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01946334792196828</v>
+        <v>0.04480913853887129</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2461,22 +2461,22 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.004683931954983655</v>
+        <v>-0.005002073693916951</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01019925570667705</v>
+        <v>-0.03269806123985818</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02529964231679951</v>
+        <v>0.03332447309181371</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.002510073240899202</v>
+        <v>-0.01057945941718841</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.003856715391578522</v>
+        <v>0.01048120496013449</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002573426201727712</v>
+        <v>0.0799985413326051</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,73 +2518,73 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.00243439873139778</v>
+        <v>0.04415565625256326</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01310225203196451</v>
+        <v>-0.03746270806686212</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.009081271683676829</v>
+        <v>-0.03111559293095422</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.002369423884026772</v>
+        <v>-0.0278319693341102</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.004779426536449403</v>
+        <v>-0.04754704398946758</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01064923798977921</v>
+        <v>-0.007582810346289737</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.002260042457627998</v>
+        <v>0.01381363895179955</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.003777627625052339</v>
+        <v>-0.03683095819889325</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01932979527461894</v>
+        <v>0.05649313831547542</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2596,10 +2596,10 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.003483882680676071</v>
+        <v>-0.03600123335165865</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001689470925475353</v>
+        <v>-0.03506875770543</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01937546147588129</v>
+        <v>0.03799460117686235</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.005590986924347763</v>
+        <v>-0.0202820860938054</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01832729441731256</v>
+        <v>-0.02042187145594127</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00717835180805337</v>
+        <v>-0.0101417731537069</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0008246658664184151</v>
+        <v>0.0109132939852579</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.008897443646165078</v>
+        <v>0.02640096333667788</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01040223952909907</v>
+        <v>-0.003030787790903877</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01277140148729668</v>
+        <v>-0.004816476232238517</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.006862994266849448</v>
+        <v>0.02326153059545248</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1047590223510288</v>
+        <v>0.06675658572729054</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.421067702996792e-11</v>
+        <v>-4.54836017795278e-11</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01221440356176937</v>
+        <v>-0.004030884592820851</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1282701407714113</v>
+        <v>-0.1198714728566038</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1283900506809031</v>
+        <v>0.1691228218764615</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05145672109429845</v>
+        <v>0.02631448402550209</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2763,16 +2763,16 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>5.137591121088987e-11</v>
+        <v>2.870161019321192e-11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.378756821078828e-11</v>
+        <v>9.410662423281797e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004191786531891463</v>
+        <v>-0.004725758486324783</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -2781,34 +2781,34 @@
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03184732930645271</v>
+        <v>0.05433314512819719</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0470981072096997</v>
+        <v>-0.03685768270225354</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06137438934728233</v>
+        <v>-0.07090190024288162</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02827985551603224</v>
+        <v>0.07749429614364371</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.06124498175978006</v>
+        <v>-0.00301066728348097</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.03365314108582015</v>
+        <v>0.05610450956867979</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,52 +2835,52 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3025063777815939</v>
+        <v>0.2124904883519416</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.005402503955723495</v>
+        <v>-0.09098827095028829</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.163019764675841</v>
+        <v>-0.0108943546442004</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.360073009133564e-12</v>
+        <v>4.16246624877719e-13</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-2.34793524074122e-11</v>
+        <v>-1.707788422461625e-12</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01158015967536422</v>
+        <v>-0.0004467056055722096</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.001472554319467655</v>
+        <v>0.006119144903805377</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.06838795741080923</v>
+        <v>0.04271490605587751</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0914517131345514</v>
+        <v>0.06084334680732134</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,16 +2925,16 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1924814695187996</v>
+        <v>0.1638315048166265</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01422246896211575</v>
+        <v>-0.0739012714005358</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0551271869399453</v>
+        <v>0.05205873342974224</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2943,25 +2943,25 @@
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.08034316485376686</v>
+        <v>-0.08186217683861222</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0171977533496869</v>
+        <v>0.05995390062221376</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.01271337634068031</v>
+        <v>-0.01419796019085159</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2973,25 +2973,25 @@
         <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02736727668040394</v>
+        <v>-0.1359920269617976</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05536899761918818</v>
+        <v>0.02328376270828122</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1106574582610274</v>
+        <v>-0.05610941803499409</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3006,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.08022453661454138</v>
+        <v>-0.09271253116759309</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03855328427152224</v>
+        <v>0.05963347767078184</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.009178141608317623</v>
+        <v>-0.01112234024112624</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,187 +3027,187 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004127040484864</v>
+        <v>-0.003007637400935095</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01737226997836223</v>
+        <v>0.02370468076134178</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.01435508980611262</v>
+        <v>-0.07595557946551929</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.100053499469</v>
+        <v>-0.04628454256291706</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02191034664890546</v>
+        <v>0.02440376887327375</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.01553719985618983</v>
+        <v>-0.05800474299630667</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01150606443260754</v>
+        <v>0.1019673263596708</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04673285093831335</v>
+        <v>0.04086516956086054</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.008999069799392873</v>
+        <v>-0.04249690941924827</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.05942758210467828</v>
+        <v>-0.01533767642488512</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.006352802296443374</v>
+        <v>0.05091721522999457</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04254555414915984</v>
+        <v>0.00373227774541949</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.08489710585789521</v>
+        <v>-0.05864193558698205</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.05922877839975663</v>
+        <v>0.06278986929280678</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01951444684597706</v>
+        <v>-0.04190081175783786</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.07710700498637499</v>
+        <v>-0.1043863289550619</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03593905473079283</v>
+        <v>0.0746601282924436</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.0105101001107204</v>
+        <v>-0.01844583869859133</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.02418150471878644</v>
+        <v>-0.00630084127030239</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0453372967470286</v>
+        <v>0.004272205919513351</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.03169326707601525</v>
+        <v>0.002480478025089378</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3216,22 +3216,22 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.06024926900248523</v>
+        <v>0.001527142338392457</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04249131445370178</v>
+        <v>0.09492024112620484</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.05228331588105373</v>
+        <v>-0.06072799293036835</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3240,7 +3240,7 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0001015899529232062</v>
+        <v>-0.05641824288248559</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.003013709358539912</v>
+        <v>0.0598703916780006</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00907168245890364</v>
+        <v>0.01917178607436619</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006447910212473201</v>
+        <v>0.006579008740276927</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003815180306606967</v>
+        <v>0.01184162584929457</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.00321648763505334</v>
+        <v>-0.02724474883163807</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002403186141633685</v>
+        <v>-0.008266470179967945</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01446950271643675</v>
+        <v>0.0362958458506668</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.000827713635172347</v>
+        <v>-0.002047263977671058</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,52 +3341,52 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-9.835019492156326e-13</v>
+        <v>-1.811002315712854e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003227579056954229</v>
+        <v>0.001457492357956901</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.008121864694251298</v>
+        <v>-0.017481791712052</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01345674514601855</v>
+        <v>-0.04607459923144255</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.00225220914553921</v>
+        <v>-0.02379072777139579</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002705242550916918</v>
+        <v>0.01247809159139688</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00327492599031249</v>
+        <v>-0.008169801815899366</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001096542103282825</v>
+        <v>-0.02902316875960798</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3413,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.02719982714002814</v>
+        <v>0.09685050229109075</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01696444549890779</v>
+        <v>-0.01238741769877918</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.009000441127803207</v>
+        <v>-0.01552586851725748</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,67 +3434,67 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0002626655730034742</v>
+        <v>-0.0005451889226572592</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-7.341860336483155e-12</v>
+        <v>-6.508964536455598e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0005191888172330452</v>
+        <v>0.02548259478923576</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.009076945208236223</v>
+        <v>0.01089313768083814</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.007610697272240174</v>
+        <v>0.04378679525234232</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.005575258925260059</v>
+        <v>0.03492769285500204</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.006178803573208058</v>
+        <v>0.03303693447223382</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.006265539492191961</v>
+        <v>-0.005021418997739656</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.004847079551335919</v>
+        <v>-0.03668080762715841</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3521,34 +3521,34 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.003289110465080887</v>
+        <v>-0.01393331002508069</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.002716789226628948</v>
+        <v>-0.003541478434033291</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006896549336821471</v>
+        <v>0.02433188235785266</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.009564449673152297</v>
+        <v>-0.02655214621140843</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
@@ -3557,52 +3557,52 @@
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003881957728018197</v>
+        <v>0.04037284141194593</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01404862673699141</v>
+        <v>0.03164253973128146</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.001761286685159005</v>
+        <v>-0.01625269032132545</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.001800169843790403</v>
+        <v>-0.005112764686521644</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.008257346552015101</v>
+        <v>0.02207432314530449</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.006062322319999503</v>
+        <v>-0.005164130278678234</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,133 +3611,133 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0003913492275769977</v>
+        <v>-0.0008809587168566303</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01202835068436257</v>
+        <v>-0.001584183316850914</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002864978799471749</v>
+        <v>-0.01442882864625355</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01015024705820974</v>
+        <v>-0.003422541200253784</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002679307825957548</v>
+        <v>0.03639141909984205</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01281737189064653</v>
+        <v>0.01058127641232502</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.006801035044213889</v>
+        <v>-0.01127989643166831</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.005734063298299779</v>
+        <v>0.02278790137504583</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.00357030700430302</v>
+        <v>-0.006989312641271804</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.003724719906701632</v>
+        <v>-0.01284570121507624</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.004325395495288836</v>
+        <v>-0.001777616242465306</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.004523809597890237</v>
+        <v>0.004294543028077898</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.002898212406854454</v>
+        <v>-0.01961993641421579</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01645330809483575</v>
+        <v>0.02753866160524488</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0004346302705885651</v>
+        <v>-0.01998131556482539</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.002054055848698319</v>
+        <v>-0.01232263276341423</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.007776608520237798</v>
+        <v>0.01805517185208332</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
@@ -3764,46 +3764,46 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0101026949256236</v>
+        <v>-0.01524322532032293</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01446568879376814</v>
+        <v>0.01304739879157475</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.003105373190848245</v>
+        <v>0.008477389457535811</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.001002030262971382</v>
+        <v>0.01655059105143318</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001210427085926816</v>
+        <v>-0.001502393727822819</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.006336389858552563</v>
+        <v>-0.03319997409873624</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,16 +3812,16 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.004082245334986453</v>
+        <v>0.009115922448743853</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,13 +3830,13 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.005050160424546781</v>
+        <v>0.01165290234972282</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03211432155177909</v>
+        <v>0.0381028896018309</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01865813242713158</v>
+        <v>-0.004150060020444287</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01231835636767514</v>
+        <v>0.008142846053437944</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01176671555696468</v>
+        <v>-0.0360035995094681</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.002490150035315973</v>
+        <v>0.008782354460828161</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,52 +3892,52 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04092925448612005</v>
+        <v>0.0115774118787762</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0007381841763497745</v>
+        <v>-0.002609301675192842</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0003469583873311182</v>
+        <v>-0.003936290543769455</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.00124542614912094</v>
+        <v>0.002061387310328518</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01643087795462955</v>
+        <v>-0.01659006365219288</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.022666632376176</v>
+        <v>-0.0195763343510953</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01829268116173023</v>
+        <v>0.002896009476765685</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01523656308516804</v>
+        <v>0.03203742899334518</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01462592904099051</v>
+        <v>-0.0006804897529636546</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01248065732713575</v>
+        <v>-0.0198016476864264</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1185750361624378</v>
+        <v>0.1178556096180219</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07992161887646369</v>
+        <v>-0.006765759070894674</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001412597894769314</v>
+        <v>0.00482064854930216</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.003174512130097024</v>
+        <v>-0.00076597519299809</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.001687941472095171</v>
+        <v>-0.002346190298834312</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02922089081445605</v>
+        <v>0.02986656678893958</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.003844187013604827</v>
+        <v>0.01666366685996415</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,61 +4045,61 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.05373535858483756</v>
+        <v>0.05058741686995014</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02680998222319885</v>
+        <v>0.0136458693484807</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.04946166235445827</v>
+        <v>0.06517332630243286</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0254053201292953</v>
+        <v>-0.01840869757592748</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01666292683843574</v>
+        <v>-0.0245717596355996</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0133229341161836</v>
+        <v>-0.03079654139791788</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.009577273529854479</v>
+        <v>-0.004608475318565224</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4111,22 +4111,22 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01869209772149522</v>
+        <v>0.01324001538743747</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.00366367113829173</v>
+        <v>-0.04613732698496126</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.002423132296382514</v>
+        <v>-0.002273061389203045</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.005766809980660703</v>
+        <v>0.03724234270226592</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01149886050931</v>
+        <v>-0.0305819948192732</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.006222718972896313</v>
+        <v>-0.005715748696935025</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02019832206340788</v>
+        <v>0.01201789563098089</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03057067236397179</v>
+        <v>-0.01868427729491209</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03726644162781242</v>
+        <v>-0.02668543635369463</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,133 +4189,133 @@
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01143107002990708</v>
+        <v>-0.001806153896667132</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.002173610500390051</v>
+        <v>-0.01849002380786375</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001392506838568294</v>
+        <v>-0.001447391008528046</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.01396591242454905</v>
+        <v>-0.007225003542604202</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.008709287338219976</v>
+        <v>0.02569566268425313</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.002609753144991111</v>
+        <v>0.00847861596458996</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01049949554763543</v>
+        <v>-0.004462234997921604</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.003426290485811819</v>
+        <v>-0.02450542134170786</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.003929569453855625</v>
+        <v>-0.01250380993229195</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.02560942234773207</v>
+        <v>0.00624169212285732</v>
       </c>
       <c r="EO7" t="n">
         <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04543417593317097</v>
+        <v>0.004180348430712513</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.002577728451845476</v>
+        <v>-0.003481109820141619</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01663892712440147</v>
+        <v>-0.01834797407575164</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.01965251143628528</v>
+        <v>-0.03524130719175043</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.004659769495664184</v>
+        <v>-0.01571805855221821</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,70 +4327,70 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01415808208996762</v>
+        <v>0.01419841737175076</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.005866773648910276</v>
+        <v>-0.02352257330033291</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01091697616682245</v>
+        <v>0.005473194431046926</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01337167971442908</v>
+        <v>0.04588875291313237</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03766043872364955</v>
+        <v>0.009693092435077266</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.03060206033006855</v>
+        <v>-0.006481319217134946</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0008150762667368274</v>
+        <v>0.002201334663556517</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03594518750750733</v>
+        <v>-0.01499815241025409</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.004320773574622363</v>
+        <v>0.01713947296947874</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3074164942345954</v>
+        <v>0.1414960270647595</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09341493104617134</v>
+        <v>-0.07912334296997466</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004674670239064709</v>
+        <v>0.04392051698608722</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5012,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.07542117018312261</v>
+        <v>-0.05653795743572259</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1341869912615439</v>
+        <v>0.157250384799392</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01291851266193206</v>
+        <v>-0.01988554094631119</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02233220189895401</v>
+        <v>0.01833950950558755</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02742237103706371</v>
+        <v>-0.0008690580043371832</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02538271151421819</v>
+        <v>0.0004663596391663828</v>
       </c>
       <c r="X9" t="n">
         <v>-0</v>
@@ -5057,7 +5057,7 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,25 +5066,25 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07611775469051614</v>
+        <v>0.03562883041053132</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003225467932423122</v>
+        <v>-0.05972180522787789</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.07491411140070604</v>
+        <v>-0.0661824620073363</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -5093,16 +5093,16 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07628572389906658</v>
+        <v>0.1175081303150854</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.09223501850750063</v>
+        <v>-0.08704086912696798</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.08544536949717943</v>
+        <v>0.1126132160725783</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,25 +5111,25 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5317713854999866</v>
+        <v>0.2353262528321284</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.06513743244709896</v>
+        <v>-0.1895791068871116</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2342374762156317</v>
+        <v>-0.01631906981220587</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5138,25 +5138,25 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.0005167597096400455</v>
+        <v>-0.006560919618508471</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.007075147866563221</v>
+        <v>0.002299238328933677</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.02636139528553031</v>
+        <v>-0.001153113856844104</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5171,25 +5171,25 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02169172162740427</v>
+        <v>-0.00803097526687558</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.06014520328497108</v>
+        <v>0.02648330547754086</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1345272154303411</v>
+        <v>0.01236800269994951</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.3325617574459699</v>
+        <v>0.1958753814010668</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.1176913149945369</v>
+        <v>-0.1887726820463456</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01533143797405323</v>
+        <v>0.06577074412765238</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5228,184 +5228,184 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1161711595516032</v>
+        <v>-0.09773312169269599</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.02635387389107502</v>
+        <v>0.1415719178012855</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.04286601132051968</v>
+        <v>-0.07272048149726645</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.07074041989946581</v>
+        <v>-0.1209733557745777</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1285288398437327</v>
+        <v>0.1674504337233746</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2113171528632981</v>
+        <v>-0.04590918509386394</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1069017878704253</v>
+        <v>-0.1043283530458304</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.06426346394443246</v>
+        <v>0.1377859312934736</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0006521649069493775</v>
+        <v>-0.06305820235762737</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01600797801108925</v>
+        <v>-0.01392048284514542</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.07389782302542051</v>
+        <v>0.05503270134856747</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09221635158958501</v>
+        <v>-0.09306510171846286</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1090411329093383</v>
+        <v>-0.06009769440958217</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.05682610736348229</v>
+        <v>0.06651887647027838</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.04692753836719188</v>
+        <v>-0.07804710610909552</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.007025311030457646</v>
+        <v>0.05750069604741034</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.07654994292295714</v>
+        <v>0.06423980150635461</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.008867357682909941</v>
+        <v>-0.004543857971703712</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.04668066978820579</v>
+        <v>-0.03271074276959516</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.02693956084076526</v>
+        <v>0.1249024683205028</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.007347152479384608</v>
+        <v>-0.01953457484004867</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,28 +5414,28 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1379833513535925</v>
+        <v>-0.0564762082548255</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06659283803671988</v>
+        <v>-0.0982444667433056</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.06569717950100426</v>
+        <v>-0.05832805505630705</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
@@ -5444,43 +5444,43 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1148811206685352</v>
+        <v>-0.1142845666609911</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.05831501288991423</v>
+        <v>0.1592639138594289</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.03244037376378027</v>
+        <v>-0.0724408383840824</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02588869626331234</v>
+        <v>-0.0446555732161408</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.06749980048397024</v>
+        <v>0.03991745154643635</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.07641861895000003</v>
+        <v>-0.04953970219654871</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5492,25 +5492,25 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.06795110494189902</v>
+        <v>0.05342879286387819</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01151451866390557</v>
+        <v>0.1513870292300104</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.08164723067236963</v>
+        <v>-0.0361011939864128</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,31 +5522,31 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.04764262769462411</v>
+        <v>-0.06928362259279111</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02385462491590652</v>
+        <v>0.09309668778643145</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1949238575876912</v>
+        <v>0.1072395286946042</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03114498496360391</v>
+        <v>-0.03168900356202093</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07923089661822807</v>
+        <v>-0.01496754024724825</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.009342831864621334</v>
+        <v>-0.009431737799738079</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01877851228479292</v>
+        <v>-0.01360906484754425</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0747743588337446</v>
+        <v>0.09253207225981802</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03751621453021287</v>
+        <v>0.0115524982683994</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.002876843763223824</v>
+        <v>-0.006322188128525858</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,25 +5608,25 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06369757708807695</v>
+        <v>0.02577509072222274</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.02272747532779318</v>
+        <v>-0.01733098268254574</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0077105335090246</v>
+        <v>-0.02411596860251135</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01745469756105694</v>
+        <v>0.00139406744934165</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.01090949819782506</v>
+        <v>-0.01517457248200579</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1010786336125553</v>
+        <v>-0.05964746947648717</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01867316016433635</v>
+        <v>-0.06881670514923439</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0161259627619541</v>
+        <v>0.01196308507819079</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,16 +5662,16 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02574990305549862</v>
+        <v>0.07107359753692777</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04601608618033447</v>
+        <v>-0.02017298904447758</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.0719721900404449</v>
+        <v>0.02671058622569352</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,34 +5680,34 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.004297196984433509</v>
+        <v>-0.01810499534677105</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3356390603101935</v>
+        <v>0.165280831362862</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0625796232022424</v>
+        <v>-0.04945215587781198</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1362480754090794</v>
+        <v>-0.1029928454835915</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.07871231897097564</v>
+        <v>-0.02515801134476349</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.002768513706732676</v>
+        <v>8.583746412701549e-05</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.02133969973055314</v>
+        <v>-0.01335927854351663</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.08180121658650671</v>
+        <v>-0.0002710899817438778</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.03509336970279404</v>
+        <v>-0.02574457674511852</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.06536543766221746</v>
+        <v>0.0302522182413181</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.145763656455779</v>
+        <v>0.02299502637066579</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.06541113298625141</v>
+        <v>0.0400397581372832</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.05418167695910962</v>
+        <v>0.0142887395482432</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,52 +5770,52 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2154047004834228</v>
+        <v>0.122187946917631</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02998234752580764</v>
+        <v>-0.04831869246606465</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.01077114859756164</v>
+        <v>-0.06897986890340903</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.008820068710335936</v>
+        <v>-0.02886945781111605</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08129824093831874</v>
+        <v>-0.05911018555116305</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01573675010557837</v>
+        <v>0.0496550855056044</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.001257268742177206</v>
+        <v>0.006103011278659406</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.007887318591604405</v>
+        <v>-0.00839725602904464</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5824,79 +5824,79 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.002549597064313447</v>
+        <v>-0.05883253653066661</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.09342829691870316</v>
+        <v>0.07558121967792708</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.0546662775309722</v>
+        <v>0.08311953290442954</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0858680542764296</v>
+        <v>0.004512708312291606</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06861693394474833</v>
+        <v>-0.06387892380652634</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.04630019861552669</v>
+        <v>0.05625699777848542</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01231364008170116</v>
+        <v>0.01593005113739449</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.003515115668967814</v>
+        <v>-0.01041952672222521</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.09632281738589744</v>
+        <v>-0.05449884230304104</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02395397350912493</v>
+        <v>0.01786519093876596</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.00298207506782805</v>
+        <v>-0.01024099851683625</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01506645766739277</v>
+        <v>-0.009610324867367378</v>
       </c>
       <c r="DM10" t="n">
         <v>0</v>
@@ -5905,70 +5905,70 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.09020795120060893</v>
+        <v>-0.0546698146712816</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.01727420716382665</v>
+        <v>0.02690154096647007</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0427616801964659</v>
+        <v>-0.03659541033108255</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.01741933451503766</v>
+        <v>0.05251919699395777</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01224083173076354</v>
+        <v>0.0779717493669249</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.01997760123415561</v>
+        <v>0.07068641127272811</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.03689832681047959</v>
+        <v>-0.01469925141926225</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.004340778207563172</v>
+        <v>0.06975810836959316</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.0474184155616106</v>
+        <v>-0.02506439015373767</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.003960614864994568</v>
+        <v>0.03079490682097445</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01948045868174289</v>
+        <v>-0.0004248506139098287</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.06985241617754509</v>
+        <v>-0.0205598673381537</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,133 +5986,133 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.08341025629410045</v>
+        <v>0.0005122738480894703</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0554721187709872</v>
+        <v>0.03223335469896229</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.08281562392342953</v>
+        <v>-0.001458230687084032</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.01364673971126911</v>
+        <v>-0.02037543079088083</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07076804765967479</v>
+        <v>-0.0748812772511674</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03345761796252057</v>
+        <v>0.06019954387864247</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.008552491990315948</v>
+        <v>0.004185049641637444</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0009320875651520778</v>
+        <v>-0.009626398056018764</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02254343497725734</v>
+        <v>-0.008069265576743964</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.06511188971024752</v>
+        <v>0.009934364532437389</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.08352713753049504</v>
+        <v>0.03188138723238729</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.005842281054725282</v>
+        <v>0.004950176817120284</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1207536911506798</v>
+        <v>0.009535809200977872</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.05964047506557543</v>
+        <v>0.0986023914307419</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.09674116651613587</v>
+        <v>-0.106747129167537</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.006983542009405877</v>
+        <v>0.02532910559419197</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02240828190059849</v>
+        <v>-0.03795905137337083</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.04036786999475693</v>
+        <v>0.005674394286438405</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02228775736387072</v>
+        <v>-0.01231651231870081</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02527182781634258</v>
+        <v>0.2910626223927827</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005103148531812541</v>
+        <v>0.05798164559513822</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.03645942080786833</v>
+        <v>-0.1989782815463915</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0004942887352872031</v>
+        <v>-0.00971723088152952</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0002734587728454436</v>
+        <v>0.002942829023919886</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009321055219299492</v>
+        <v>0.05963207462015739</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.009311291959372336</v>
+        <v>0.1025252091083143</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,52 +6186,52 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.001707484555018416</v>
+        <v>-0.05199460581044359</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003390583600845882</v>
+        <v>-2.149669444052214e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01221316796922605</v>
+        <v>-0.09930454182506944</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01781000755768598</v>
+        <v>-0.2320220937982311</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001339823274388302</v>
+        <v>0.1021058953423038</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001834663845924749</v>
+        <v>0.119796472172972</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,43 +6240,43 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.00887673943388689</v>
+        <v>0.0599281607620195</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.0062577994922707</v>
+        <v>-0.03291281198581725</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.04171305763163554</v>
+        <v>0.3167514026932489</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01481848845429409</v>
+        <v>-0.2061978898147576</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.007101885675776443</v>
+        <v>-0.08475579050014669</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
@@ -6285,52 +6285,52 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.007083798773765775</v>
+        <v>0.04642948264657372</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.006662519829755887</v>
+        <v>0.01104917860106639</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.02076713732021096</v>
+        <v>-0.0733725551768336</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0325128744668122</v>
+        <v>-0.00386585111340135</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.008043236239876747</v>
+        <v>0.09954458245562969</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.003250167010372724</v>
+        <v>0.12201060492344</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.01299866386736707</v>
+        <v>0.341062570742786</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,94 +6348,94 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0006467004295372201</v>
+        <v>0.02555406704146935</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.005270244602268396</v>
+        <v>-0.1307984136902994</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.001337095902199276</v>
+        <v>-0.1528095292310003</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.00464611600510487</v>
+        <v>-0.06358954118111437</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01685776153972063</v>
+        <v>0.1294428623567939</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.004079293048314576</v>
+        <v>-0.1161354186231855</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.00999404660924226</v>
+        <v>0.04210110983911319</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01510548099276317</v>
+        <v>0.04351250234218767</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.001905780870976901</v>
+        <v>-0.1381845979850248</v>
       </c>
       <c r="CX11" t="n">
         <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.0004267751575013701</v>
+        <v>-0.03530756156304545</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01491322002238111</v>
+        <v>0.1410405060745226</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
@@ -6444,82 +6444,82 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.00419493575303595</v>
+        <v>-0.1575126150434193</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01042563186418663</v>
+        <v>-0.1579448757287264</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01189505640312133</v>
+        <v>0.1309629277939304</v>
       </c>
       <c r="DK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.001786912834538432</v>
+        <v>-0.0916471566097804</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01004271449431568</v>
+        <v>0.03610914518366896</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.009004453197220187</v>
+        <v>0.0658489588510716</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.0133584167880645</v>
+        <v>-0.01711335921459019</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01534191556655579</v>
+        <v>0.03673013196624247</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.007329903017803468</v>
+        <v>0.1524424825830215</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
@@ -6528,34 +6528,34 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.0001142359007693035</v>
+        <v>-0.0231432106503556</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.005969661170169345</v>
+        <v>-0.08088337950540819</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01124121991541926</v>
+        <v>0.02212098505243623</v>
       </c>
       <c r="EL11" t="n">
         <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.003940011516657378</v>
+        <v>-0.07616978308638499</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,16 +6564,16 @@
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.001071998945759593</v>
+        <v>-0.2531767656425268</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02417692945130313</v>
+        <v>0.1206578146853547</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>-0</v>
@@ -6582,19 +6582,19 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.00400579663910141</v>
+        <v>-0.1580864904076252</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.001733270420803214</v>
+        <v>-0.08642214210592236</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01683109116464705</v>
+        <v>0.1104247803548835</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
@@ -6606,10 +6606,10 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.002584715287659414</v>
+        <v>-0.2022794436790029</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02178602106301987</v>
+        <v>0.09047803132732921</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.004007797275748915</v>
+        <v>0.1793729261081488</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.002381027121123677</v>
+        <v>0.026891739177902</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.003152508077921613</v>
+        <v>-0.01514297568876039</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01683238647885475</v>
+        <v>-0.06904486738799989</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02017105374383327</v>
+        <v>-0.01487674175834094</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.001920558501812165</v>
+        <v>0.1482551055518672</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,43 +6692,43 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.179057703084732</v>
+        <v>0.1941238973989291</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.05558065897604197</v>
+        <v>-0.0950865342148742</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04059605509819462</v>
+        <v>0.006534073778643351</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006646660010186468</v>
+        <v>0.01123082079384075</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04201315394694989</v>
+        <v>0.08415203990158389</v>
       </c>
       <c r="N12" t="n">
-        <v>0.001047150342291244</v>
+        <v>0.0004840704105787979</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0404070191828752</v>
+        <v>0.05084037674339983</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.002387053340851812</v>
+        <v>-0.0107031639990193</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01594048126486085</v>
+        <v>-0.008615842017183342</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,43 +6773,43 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03685754622237068</v>
+        <v>-0.02999288658999665</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01107381203883821</v>
+        <v>-0.08602016747375532</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003782447993483443</v>
+        <v>-0.07270605576228195</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02172785289946226</v>
+        <v>0.09432652962385413</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.03545205452821976</v>
+        <v>-0.08168020350064735</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04302159777676151</v>
+        <v>0.08028761204749094</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,34 +6818,34 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2703417742115063</v>
+        <v>0.2251457485742342</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02774174471132565</v>
+        <v>-0.1176452625877232</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08278432767340703</v>
+        <v>-0.08025501383021924</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.002156827818627739</v>
+        <v>-0.007375332569566909</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02178526599238468</v>
+        <v>0.004508644823401051</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.04605738949829271</v>
+        <v>0.006119029516983383</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04954388051248602</v>
+        <v>-0.02184194180800378</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.03465274244737051</v>
+        <v>0.04598090187502039</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0868669161088883</v>
+        <v>0.06982872890887586</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1641965637135762</v>
+        <v>0.2179555366326615</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.004276743072890333</v>
+        <v>-0.1071712503250873</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02172081530906695</v>
+        <v>0.00119733655486428</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05209855873719033</v>
+        <v>-0.09736499662727252</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.001196112744174317</v>
+        <v>0.1009749326642174</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01061292794628031</v>
+        <v>-0.0200915781013824</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.02143532233217262</v>
+        <v>-0.08229470428777211</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.08323489486145619</v>
+        <v>0.09934767765722201</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1060004608147263</v>
+        <v>-0.008797920964068335</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03671194135407171</v>
+        <v>-0.1034097716900264</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01344640472267873</v>
+        <v>0.09999930275814681</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.005658107358652037</v>
+        <v>-0.005563322143408265</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,31 +7007,31 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04240421817716705</v>
+        <v>-0.09347548166262608</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.009878522023989764</v>
+        <v>0.0224076498092625</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03751443879591861</v>
+        <v>-0.0434674736504796</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,151 +7043,151 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.069047653198428</v>
+        <v>-0.07056869091737041</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03038882862172606</v>
+        <v>0.0273249878525641</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01319929464384162</v>
+        <v>-0.0004511174178352227</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01273588766139809</v>
+        <v>0.04091841791169733</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.05076018916044874</v>
+        <v>-0.1136456560479446</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.008355395132737187</v>
+        <v>0.07748729784485563</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02952552710956375</v>
+        <v>-0.03429442879001961</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02817614105982076</v>
+        <v>0.05927244896949802</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01920019486426637</v>
+        <v>0.005182113630019157</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.05926352405389873</v>
+        <v>-0.05153937881968622</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.002407886373593612</v>
+        <v>0.06236339573148444</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01299695881763458</v>
+        <v>-0.03295042033414389</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03918079164531709</v>
+        <v>-0.1151102971195147</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01779762568562731</v>
+        <v>0.1129666195653534</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01243797696115442</v>
+        <v>-0.02564610372925147</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.03192868437423697</v>
+        <v>-0.07402411784678167</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.04482164634306794</v>
+        <v>0.0261623596161783</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.005387321960322792</v>
+        <v>0.04852860280304763</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7199,61 +7199,61 @@
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0297976237589402</v>
+        <v>0.002909691651126213</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01373378704100298</v>
+        <v>0.1572646422372812</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.07035325472313568</v>
+        <v>-0.01217045684827887</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.02293622947466191</v>
+        <v>-0.06442699382573974</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04324805030302344</v>
+        <v>0.04300535990500427</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05007779304031933</v>
+        <v>0.3742250697154688</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01054906574957029</v>
+        <v>0.04084034604431774</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07564314387919324</v>
+        <v>-0.2702935281510733</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004621447042429646</v>
+        <v>0.05430932941623906</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002447002989517753</v>
+        <v>-0.004786682089348588</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006017771908539481</v>
+        <v>0.02327758437759612</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7312,79 +7312,79 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0039141919758399</v>
+        <v>0.1108608156817956</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01993787625481741</v>
+        <v>-0.07975323100508239</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003349317665797206</v>
+        <v>0.01430380015873447</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01192329041052107</v>
+        <v>-0.07191474308141836</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02306036339754872</v>
+        <v>-0.2691228356362479</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.009545907407965584</v>
+        <v>-0.05152788469718345</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01401268533857203</v>
+        <v>0.1921762484850104</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.008972330813739535</v>
+        <v>0.1437162604793143</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.017584057038823</v>
+        <v>-0.180070702316088</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.06188319872505958</v>
+        <v>0.4676631767615793</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -7405,10 +7405,10 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001984766561966509</v>
+        <v>-0.2781170866130205</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.03618383507946013</v>
+        <v>-0.1896549970636888</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01423338432031802</v>
+        <v>0.001533661373275363</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.005340084305939117</v>
+        <v>-0.08321752163187865</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.02169529952862786</v>
+        <v>-0.1553110610559389</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03706610015735281</v>
+        <v>-0.03769298728740071</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,40 +7459,40 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.00137886763856877</v>
+        <v>0.09436239037862469</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01270147721912102</v>
+        <v>0.04002123516456419</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03098190261392727</v>
+        <v>0.3761215860448202</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01309011307327854</v>
+        <v>-0.03378845956365425</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.008454670957304176</v>
+        <v>-0.2374664430157531</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.004026054302841274</v>
+        <v>-0.2161976336967314</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -7513,10 +7513,10 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01439455478993529</v>
+        <v>-0.0218986712083269</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02943491584799763</v>
+        <v>0.1846736856298272</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,25 +7525,25 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.002744097054387966</v>
+        <v>-0.2308361482540826</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.004421283151622923</v>
+        <v>0.3561514845284611</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02991318706183083</v>
+        <v>0.3774211508031581</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.0009843034069631272</v>
+        <v>-0.1967339121303224</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.009605319437846099</v>
+        <v>-0.01899937466407169</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03037602462605556</v>
+        <v>0.1654223699422648</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,46 +7585,46 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.005321917088333096</v>
+        <v>-0.07310574552081769</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.008656188662753677</v>
+        <v>-0.1452236996350316</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.00425153414170033</v>
+        <v>0.1057357149313698</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01368033490258256</v>
+        <v>-0.09057405113817261</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01830839338044751</v>
+        <v>-0.04148712797178136</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.001764884285027933</v>
+        <v>0.08955161996954733</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7639,34 +7639,34 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01612016922130185</v>
+        <v>0.09114174376071278</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.008038264709685964</v>
+        <v>0.005219144599889708</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0008397140750411004</v>
+        <v>0.2133290180494235</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.001335575368012285</v>
+        <v>-0.07352219945392913</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,43 +7675,43 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.00393921668131074</v>
+        <v>-0.0780085493044913</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0336732973658762</v>
+        <v>0.01630414059636706</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.004911591455929957</v>
+        <v>-0.113191220692946</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02455586964675239</v>
+        <v>-0.1653656319092272</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.05776829604457789</v>
+        <v>0.09874322038805058</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
@@ -7720,19 +7720,19 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0002625791468348909</v>
+        <v>-0.2253327223515959</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01184378480620015</v>
+        <v>-0.06443365272710135</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0315454843573584</v>
+        <v>0.1536632631766075</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7744,22 +7744,22 @@
         <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01828416510843671</v>
+        <v>-0.1674197999784489</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.00884936757940173</v>
+        <v>0.1454803514719366</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0131190577481996</v>
+        <v>-0.06347102535916738</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7774,19 +7774,19 @@
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.001289467842618323</v>
+        <v>0.04286886152227109</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.004532772300735254</v>
+        <v>0.1364582658539795</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.005025939685359677</v>
+        <v>0.003631214738058651</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,13 +7795,13 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.01310175628291698</v>
+        <v>-0.06329155183341305</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
@@ -7813,13 +7813,13 @@
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01083441456026264</v>
+        <v>0.05944752439021239</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,22 +7830,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3743193515911779</v>
+        <v>0.2146572976648557</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1005645864007494</v>
+        <v>-0.08191333418076419</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01266879395680505</v>
+        <v>-0.03359431161951782</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -7854,19 +7854,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.04411592312176861</v>
+        <v>0.0393393498818256</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04058206689843002</v>
+        <v>0.04134470988795832</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.004327172684046868</v>
+        <v>-0.006530967955358893</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,22 +7881,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1143402732116307</v>
+        <v>0.0259282709056588</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.02776560918484423</v>
+        <v>-0.01115588452073319</v>
       </c>
       <c r="W14" t="n">
-        <v>0.003921963410133611</v>
+        <v>-0.04081702851269581</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7908,55 +7908,55 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.034030029285428</v>
+        <v>-0.01764861880314191</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01933465556032977</v>
+        <v>-0.06942409655521245</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01951619847666063</v>
+        <v>-0.06752857508227822</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.03794212496255338</v>
+        <v>0.1008190489639958</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06838975265464836</v>
+        <v>-0.02416151814791387</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.04982647368909352</v>
+        <v>0.0615287431271252</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,25 +7965,25 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4035924967114521</v>
+        <v>0.2259287740631408</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02170152623225912</v>
+        <v>-0.03872571992308745</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.132410953067056</v>
+        <v>-0.08866544188635678</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,16 +7992,16 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0209002513132526</v>
+        <v>-0.009148405168008553</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.04228050037332897</v>
+        <v>-0.007050262708808778</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.07870231021521754</v>
+        <v>-0.01570669467983332</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8010,31 +8010,31 @@
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.08771199059844108</v>
+        <v>-0.02350508178514557</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0562732221129784</v>
+        <v>0.01364466227388479</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1394501225619905</v>
+        <v>0.07281842998747963</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,19 +8046,19 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.249151516727693</v>
+        <v>0.1831654132859381</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01926106791242726</v>
+        <v>-0.0859585664603108</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.05079753823878407</v>
+        <v>-0.01508115669559783</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,22 +8067,22 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1042733716709371</v>
+        <v>-0.1028741096072388</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.01501755107066117</v>
+        <v>0.06529538174587507</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02686593633488366</v>
+        <v>0.01570689257198363</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8094,49 +8094,49 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.01519892187788089</v>
+        <v>-0.07438486706161192</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.0794814897876307</v>
+        <v>0.1083643259963043</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1169072747513461</v>
+        <v>0.02296228640274509</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.09242146130369379</v>
+        <v>-0.1003298811340494</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.03190055326482938</v>
+        <v>0.06702562301730093</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02835607320628163</v>
+        <v>0.01622653101300922</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.004914283446959852</v>
+        <v>0.00310113863130832</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.02703554534200887</v>
+        <v>0.01195665246314942</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0416598878403756</v>
+        <v>-0.03143690262900293</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,79 +8181,79 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.07829971832212836</v>
+        <v>-0.06085479572375022</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.00795865805094482</v>
+        <v>-0.01178671865193146</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03096732837779371</v>
+        <v>-0.02043453878989292</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.03252234843670397</v>
+        <v>0.08089128014993614</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.002623193246797292</v>
+        <v>0.04326233545948036</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.07762706143819127</v>
+        <v>-0.05418601515859536</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.07493438974782489</v>
+        <v>-0.06617175788276282</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02645106746420135</v>
+        <v>0.06528102303222631</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.008196329308332306</v>
+        <v>0.02791509622690765</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.06940558461719064</v>
+        <v>-0.0372618322923701</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.04062240551551103</v>
+        <v>0.06099333899573915</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.03254308031319406</v>
+        <v>-0.01478461177888063</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,79 +8286,79 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.09438386436581098</v>
+        <v>-0.1069447671467327</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02423872308956363</v>
+        <v>0.07291163416020452</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.0181587683924258</v>
+        <v>-0.0006004343891678221</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01182207684847068</v>
+        <v>-0.02915255032219688</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01663798251865446</v>
+        <v>0.01605593353988812</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03813748395499191</v>
+        <v>-0.02636615508526232</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.003291821387888793</v>
+        <v>0.01061569462804261</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0005745135726460095</v>
+        <v>0.08664216106431759</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.001949551378640368</v>
+        <v>-0.009997004314373805</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
@@ -8367,31 +8367,31 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.01359856473351841</v>
+        <v>-0.07915528770694846</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.04377406826714676</v>
+        <v>0.01570091858572066</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4388211964457429</v>
+        <v>0.3900465227961987</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1218425185198898</v>
+        <v>-0.1523596586077099</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08540686289176971</v>
+        <v>-0.002046397806758902</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
@@ -8426,49 +8426,49 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1243109113441424</v>
+        <v>0.1384699853312863</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05117174064583307</v>
+        <v>0.07043144781127642</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.01906684244997172</v>
+        <v>-0.006290834120117304</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1621114424947721</v>
+        <v>0.09998806240310808</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0281950731428919</v>
+        <v>-0.02880872783921848</v>
       </c>
       <c r="W15" t="n">
-        <v>0.09436106228426988</v>
+        <v>-0.06243055417386098</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>-0</v>
@@ -8477,52 +8477,52 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1459535117536978</v>
+        <v>-0.04340889376555832</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.04853207590519955</v>
+        <v>-0.1628585228041391</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.02938176661209048</v>
+        <v>-0.04363849671124346</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.07208401930385602</v>
+        <v>0.1840410316372787</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.04426025404094739</v>
+        <v>-0.07613085986563313</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.03557415237358803</v>
+        <v>0.1241682864778909</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8534,22 +8534,22 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.456198259663287</v>
+        <v>0.3808354809825128</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.009130371535661239</v>
+        <v>-0.1432514868567478</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1249270366666967</v>
+        <v>-0.1151008130964546</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03679241971460735</v>
+        <v>-0.03266651070698437</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.03481922215939829</v>
+        <v>-0.00783794810823729</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1416878269222811</v>
+        <v>-0.02586889300522625</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,22 +8588,22 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.005212196756841613</v>
+        <v>-0.01195916690963357</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.05970864518148444</v>
+        <v>0.01992735009269328</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0500127714189022</v>
+        <v>0.05373284469224765</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,76 +8615,76 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3121173652447228</v>
+        <v>0.3668564677691253</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.04193154382975608</v>
+        <v>-0.1263980382942739</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08007578505260053</v>
+        <v>-0.01338675411392098</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1207309283181497</v>
+        <v>-0.1617738327742315</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.03190375901582785</v>
+        <v>0.1438163983385437</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.03081760278052562</v>
+        <v>-0.03842395480872646</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.06417718830189151</v>
+        <v>-0.1563012303886904</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.07725371035573846</v>
+        <v>0.1834789971811151</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1932587229952875</v>
+        <v>0.02112628323876495</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
         <v>-0</v>
@@ -8696,22 +8696,22 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1123398300874388</v>
+        <v>-0.1522221591794411</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04521344291658282</v>
+        <v>0.1406410412448731</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.02248082972006972</v>
+        <v>-0.0202457347563452</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
@@ -8720,25 +8720,25 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05678727132339498</v>
+        <v>-0.04574137701367405</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.02336023222766307</v>
+        <v>0.02141739339409299</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0002270466359257233</v>
+        <v>0.00322035966497825</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
@@ -8750,19 +8750,19 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.07910107526561207</v>
+        <v>-0.09561227061831248</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.007579799349530753</v>
+        <v>0.05623016925345568</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.09103082719173956</v>
+        <v>-0.02279043630526104</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
@@ -8777,43 +8777,43 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.108106423222479</v>
+        <v>0.01378085078429292</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.02855544531002914</v>
+        <v>-0.0856649259784408</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.01168743399480301</v>
+        <v>0.07779956518881655</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.05609733717292423</v>
+        <v>-0.1064501442708516</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.04977143995591936</v>
+        <v>0.1278886765683984</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.04615442148878053</v>
+        <v>-0.003804236847012988</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
@@ -8822,31 +8822,31 @@
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.06874145655877079</v>
+        <v>-0.113519577533804</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.02854858086413556</v>
+        <v>0.07604905167041175</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0334417424932234</v>
+        <v>-0.002189646857185497</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8855,25 +8855,25 @@
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1237033470265319</v>
+        <v>-0.178213470391958</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.05568962199300655</v>
+        <v>0.1522280169010791</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.03546435816912003</v>
+        <v>-0.04204168800204267</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,82 +8885,82 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.009153718639000209</v>
+        <v>-0.09810166670958238</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.06566307982452435</v>
+        <v>0.06565346654508884</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04435073241227628</v>
+        <v>-0.01575436961684495</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01556357366105037</v>
+        <v>-0.01697281248981447</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.1691495736589476</v>
+        <v>-0.1392719008779687</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01967458937509689</v>
+        <v>-0.01148513780769735</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.06122338611806851</v>
+        <v>-0.1448031311448522</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.06025242288343506</v>
+        <v>0.08726055116937695</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -9534,22 +9534,22 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.07041854567951854</v>
+        <v>0.6921540655528716</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04276080598487961</v>
+        <v>0.1615056314651589</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.03448991501585132</v>
+        <v>-0.5126915503196952</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9561,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01918446032559972</v>
+        <v>0.3435841206098446</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,10 +9573,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02016488248016724</v>
+        <v>-0.02273161357533989</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.002415639756009358</v>
+        <v>-0.04615758825648204</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9588,37 +9588,37 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.001422112321366846</v>
+        <v>0.2011848078779573</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01512137484773312</v>
+        <v>-0.1755305513387679</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02194889142196481</v>
+        <v>-0.07755186426924385</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02052853937479434</v>
+        <v>-0.02801959066827825</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -9627,10 +9627,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01833002718512783</v>
+        <v>-0.3663321445173358</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.008718069630720216</v>
+        <v>0.01522881440633982</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -9639,13 +9639,13 @@
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01147164167603195</v>
+        <v>0.2145096923733283</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -9654,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01510961600197606</v>
+        <v>0.1018006387196487</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01086246037456286</v>
+        <v>-0.1910498032329608</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,37 +9669,37 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.05205667706959215</v>
+        <v>0.7322946677716292</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.02858743586049714</v>
+        <v>-0.2096577525104323</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.004867952513343496</v>
+        <v>-0.4284959538073818</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.02874893433471825</v>
+        <v>0.02927921271735398</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,10 +9708,10 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.02180477298789317</v>
+        <v>-0.03606945434670972</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01375656844858913</v>
+        <v>-0.1110889439839104</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
@@ -9723,28 +9723,28 @@
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0402516855643156</v>
+        <v>0.01259220446008327</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.02494271936883833</v>
+        <v>0.1175433640258831</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01349132684054652</v>
+        <v>0.1587060623828556</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.03568310809729451</v>
+        <v>0.5898059517047854</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,37 +9762,37 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.009974248178150139</v>
+        <v>0.0006661211960891737</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.01441244178026927</v>
+        <v>-0.3441155475921035</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.008611055526533936</v>
+        <v>-0.2650644068612381</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.008630306697097589</v>
+        <v>-0.1002860419310075</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.009882756743934016</v>
+        <v>0.2527259674561995</v>
       </c>
       <c r="CJ17" t="n">
         <v>0</v>
@@ -9801,13 +9801,13 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.008961632045336697</v>
+        <v>-0.2874560701430511</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,10 +9816,10 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.002664999368701173</v>
+        <v>0.08083327842176372</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.0189736864903143</v>
+        <v>0.2337244479190363</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,85 +9828,85 @@
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.004099764003274066</v>
+        <v>-0.2473403218637903</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>-0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.01076196394330022</v>
+        <v>-0.07927402084578024</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.01453482255229994</v>
+        <v>0.2623917373726296</v>
       </c>
       <c r="DB17" t="n">
         <v>-0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.002708951022966143</v>
+        <v>-0.05740205177377776</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01827369814223722</v>
+        <v>-0.2766557935642747</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.002855155447541098</v>
+        <v>0.07437649051011966</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.0144376802423754</v>
+        <v>-0.08307271464959615</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01599098606205232</v>
+        <v>-0.02126051234065438</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.01254204876073749</v>
+        <v>0.0619379040031193</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>-0</v>
@@ -9915,25 +9915,25 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.00306985603878843</v>
+        <v>0.03436493470233229</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02182167655902783</v>
+        <v>0.02831508097902433</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.01877489372909164</v>
+        <v>0.1575311000024509</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
@@ -9942,52 +9942,52 @@
         <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.00135489638653182</v>
+        <v>-0.09898073604233898</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0006678494162960995</v>
+        <v>-0.1835126659985415</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.01265159192503906</v>
+        <v>0.07915393289612431</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.004246568057040912</v>
+        <v>-0.1522496242911554</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01753762879933208</v>
+        <v>-0.248271007177655</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.01420291357370249</v>
+        <v>0.2161081758086129</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
         <v>0</v>
@@ -9996,19 +9996,19 @@
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.002627851761271225</v>
+        <v>-0.2776743039952409</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.008571799232864229</v>
+        <v>-0.1549054130488606</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.01632437512518428</v>
+        <v>0.2286934659457463</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -10020,10 +10020,10 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01085019116500442</v>
+        <v>-0.3064263719451297</v>
       </c>
       <c r="FI17" t="n">
         <v>0</v>
@@ -10032,70 +10032,70 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.03239541369999967</v>
+        <v>0.0294557153899869</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01676653891482683</v>
+        <v>0.3611431608163539</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.001858082844007534</v>
+        <v>-0.02038597567569039</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0001459296042515728</v>
+        <v>-0.004359247475869218</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.002930839238697177</v>
+        <v>0.05726475444491971</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01889523361399677</v>
+        <v>-0.09533639104674477</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01099495732083293</v>
+        <v>0.1483703739248912</v>
       </c>
       <c r="GE17" t="n">
         <v>0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10103,28 +10103,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08877833924555664</v>
+        <v>0.1640533448859394</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04446934124482185</v>
+        <v>0.01596675525644581</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01985085272268796</v>
+        <v>-0.07687368335421951</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -10133,22 +10133,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02961278103150861</v>
+        <v>0.1055998891172665</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02116197723243367</v>
+        <v>-0.01297005204407345</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0006190800467525283</v>
+        <v>-0.00285847305163194</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10157,28 +10157,28 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0084893609546945</v>
+        <v>0.04599286011715191</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.009246881956212823</v>
+        <v>-0.057880745158402</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02152762153384739</v>
+        <v>0.006778515411273102</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -10187,7 +10187,7 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01975111664260675</v>
+        <v>-0.02969840739132657</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -10196,25 +10196,25 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01681542677376585</v>
+        <v>-0.07224990212691774</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.009174668573519262</v>
+        <v>-0.01222861791595267</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01455850467467693</v>
+        <v>0.04478789335574435</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
@@ -10223,16 +10223,16 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01668442175040479</v>
+        <v>-0.004802010900501488</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01265847416729718</v>
+        <v>-0.04567340542725774</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -10241,34 +10241,34 @@
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.07345685846882351</v>
+        <v>0.1865290543804013</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.03144046500151488</v>
+        <v>-0.03977802491681733</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.001671044749558859</v>
+        <v>-0.03002485486642681</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02944109642778267</v>
+        <v>-0.004735025284202804</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,10 +10277,10 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.0268451567447865</v>
+        <v>-0.03272438552664268</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.02635909745177401</v>
+        <v>-0.06875723280410645</v>
       </c>
       <c r="BI18" t="n">
         <v>-0</v>
@@ -10292,28 +10292,28 @@
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.03480107899621444</v>
+        <v>0.02126759991328063</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02758123969187382</v>
+        <v>0.0804588209604484</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01153581761683916</v>
+        <v>0.09041473094460561</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
         <v>0</v>
@@ -10322,61 +10322,61 @@
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0452726762743703</v>
+        <v>0.1488897279300981</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.003064323152637533</v>
+        <v>-0.01528175869030706</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.01270934978757614</v>
+        <v>-0.03848146321994624</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
         <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.01310460350038499</v>
+        <v>-0.05073450847092758</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.006331917465452871</v>
+        <v>-0.008472717131243949</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.01002032160650301</v>
+        <v>0.05684274715070239</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
       </c>
       <c r="CK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL18" t="n">
         <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.02564510775510228</v>
+        <v>-0.06266868678557422</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,64 +10385,64 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.002359774274639662</v>
+        <v>0.03234206209422159</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01353445967283454</v>
+        <v>0.02139266055505797</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.008092474062298682</v>
+        <v>-0.04970774141792941</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.009807911798647864</v>
+        <v>-0.01326766186866044</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.01192015604043141</v>
+        <v>0.05756126706568969</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.004981283480631214</v>
+        <v>-0.02845909671157196</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.003590181564720567</v>
+        <v>-0.01333844983609</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.001563816914731223</v>
+        <v>0.001607990276034771</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,31 +10451,31 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.005003262186655477</v>
+        <v>-0.013979992001684</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.00133529032755478</v>
+        <v>0.0005180441961292649</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.01581841308676644</v>
+        <v>-0.03773235246705126</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>-0</v>
@@ -10484,19 +10484,19 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.004859067397835357</v>
+        <v>0.01236837728076392</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.03062750162122077</v>
+        <v>-0.008855181323015902</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.01807467550615735</v>
+        <v>0.03102487311926483</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10511,7 +10511,7 @@
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01071583598840454</v>
+        <v>-0.02240004914058435</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
@@ -10520,64 +10520,64 @@
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.007259950332091567</v>
+        <v>-0.02734747468584777</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.002919550630913587</v>
+        <v>0.02089033865142293</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.0006664433510864164</v>
+        <v>-0.01859752307801006</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.01139312301820465</v>
+        <v>-0.03566461696649732</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.01158769626503037</v>
+        <v>0.04749095044776844</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
       </c>
       <c r="EV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.01056723944547273</v>
+        <v>-0.04662510254550274</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.008575501604493189</v>
+        <v>-0.02977029074999938</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.01384710593178252</v>
+        <v>0.03990768454882928</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01235264831950694</v>
+        <v>-0.07295995356636892</v>
       </c>
       <c r="FI18" t="n">
         <v>0</v>
@@ -10601,25 +10601,25 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.0265059629771339</v>
+        <v>-0.01377170349364163</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01963442309272521</v>
+        <v>0.03620100323372234</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.004767391533324688</v>
+        <v>-0.007831728894150302</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,43 +10628,43 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.0002263446708751271</v>
+        <v>-0.003178714415589739</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.004135696263798475</v>
+        <v>-0.01052734437730775</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.0249426801703967</v>
+        <v>-0.03183683790097047</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.007819773024934541</v>
+        <v>0.04163136703955109</v>
       </c>
       <c r="GE18" t="n">
         <v>0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
         <v>0</v>
@@ -11244,19 +11244,19 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3099996325487955</v>
+        <v>0.3496924948209171</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1520473430676675</v>
+        <v>-0.07066862840866595</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07948738901412787</v>
+        <v>0.02197810577889776</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.05706306293123509</v>
+        <v>-0.1060353455375801</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -11265,106 +11265,106 @@
         <v>-0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1633377197699055</v>
+        <v>0.279402406968584</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.09694810127962389</v>
+        <v>-0.08290086678168367</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.04905049095310452</v>
+        <v>-0.03819901420211574</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.01739968377037905</v>
+        <v>-0.01869744243328749</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06778747530504935</v>
+        <v>0.05074356883414192</v>
       </c>
       <c r="U20" t="n">
         <v>-0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01277104845864213</v>
+        <v>-0.08112998132394891</v>
       </c>
       <c r="W20" t="n">
-        <v>0.03801282308240116</v>
+        <v>-0.05490426138859338</v>
       </c>
       <c r="X20" t="n">
-        <v>0.05166093139754185</v>
+        <v>-0.04055783195541442</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.04645003496008007</v>
+        <v>-0.03572308210835793</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.04578744227504315</v>
+        <v>-0.1589460230143094</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.004179373705178504</v>
+        <v>-0.1104853741570418</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.006664650630156319</v>
+        <v>-0.04111754392842877</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.0002630659017314988</v>
+        <v>0.1070480376558273</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.03062671145789368</v>
+        <v>-0.05575316592547826</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.04210373138906165</v>
+        <v>0.06440617187805781</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.02947037723358778</v>
+        <v>-0.0906166159573624</v>
       </c>
       <c r="AQ20" t="n">
         <v>-0</v>
@@ -11373,25 +11373,25 @@
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.2941186288824618</v>
+        <v>0.2837090423896416</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.01692227407602446</v>
+        <v>-0.009640213656640983</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.04065886128373997</v>
+        <v>-0.06859510638902959</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.04399030655613984</v>
+        <v>-0.09779485629876186</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -11403,103 +11403,103 @@
         <v>-0</v>
       </c>
       <c r="BC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.005595269159565522</v>
+        <v>-0.004745367356232022</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.03909333742096237</v>
+        <v>-0.07403906818017626</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.09298057286533257</v>
+        <v>-0.04925628174567016</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.06281845658734803</v>
+        <v>-0.02049320995192477</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.06813108831518848</v>
+        <v>0.01170234985474954</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.06105847445403056</v>
+        <v>0.004977547382759961</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.07170751362502967</v>
+        <v>0.08326952878775615</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.02145254575782661</v>
+        <v>0.01706052450878589</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.1672274515514129</v>
+        <v>0.201368485997835</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.03049336237416117</v>
+        <v>-0.03952247382476279</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.01024942354970984</v>
+        <v>-0.009741511598862888</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.03791817339779943</v>
+        <v>-0.0949440537219986</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
       </c>
       <c r="CB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC20" t="n">
         <v>-0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.0625915836504876</v>
+        <v>-0.1004087819739758</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.0127271235749649</v>
+        <v>0.03428210223465494</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.006476174901930121</v>
+        <v>0.01302359452539014</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.03369012431948333</v>
+        <v>0.04012688801154779</v>
       </c>
       <c r="CJ20" t="n">
         <v>-0</v>
@@ -11511,25 +11511,25 @@
         <v>0</v>
       </c>
       <c r="CM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.03064902272412317</v>
+        <v>-0.08923972831380519</v>
       </c>
       <c r="CO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.08886404582336595</v>
+        <v>0.09328946371770591</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.07810973452156005</v>
+        <v>0.1181607260228007</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.07323239157647458</v>
+        <v>0.08661760648782897</v>
       </c>
       <c r="CS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT20" t="n">
         <v>-0</v>
@@ -11538,22 +11538,22 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.05085865427141057</v>
+        <v>-0.09508080942061806</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.03463164200354774</v>
+        <v>0.02634718049410619</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.00521556552026968</v>
+        <v>0.011774102734365</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.0431147117481105</v>
+        <v>0.0417524649315099</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
@@ -11565,247 +11565,247 @@
         <v>0</v>
       </c>
       <c r="DE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.007632717204868939</v>
+        <v>-0.03108692527340686</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.0732837731701485</v>
+        <v>-0.044009824967375</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.005767680036884574</v>
+        <v>0.104861708723582</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.004554382362190317</v>
+        <v>-0.006785558575344006</v>
       </c>
       <c r="DK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
         <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.01801918502989224</v>
+        <v>-0.08597538712926373</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.04399165542017191</v>
+        <v>0.03377512452335588</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.0008517988928601302</v>
+        <v>-0.01232952306729009</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.01365255598983598</v>
+        <v>0.007965912965329553</v>
       </c>
       <c r="DT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="n">
         <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
         <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.01748528585245597</v>
+        <v>0.0637598246943322</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.004184540656828695</v>
+        <v>0.01180198853147689</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.03517517422446546</v>
+        <v>0.001287240228435965</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.005342607649196261</v>
+        <v>0.02633089472041544</v>
       </c>
       <c r="EC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.08575205836553199</v>
+        <v>-0.06421736736981433</v>
       </c>
       <c r="EH20" t="n">
         <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.05425248413435411</v>
+        <v>0.04840018438457434</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.05182269844287034</v>
+        <v>0.02938821201280545</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.001135052737882999</v>
+        <v>0.0007249899937143758</v>
       </c>
       <c r="EL20" t="n">
         <v>-0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.04241188184384859</v>
+        <v>-0.02832101012125658</v>
       </c>
       <c r="EQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.01322707923719843</v>
+        <v>0.01249615668341527</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.01436755760219574</v>
+        <v>0.004893719006021037</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.07622966246784686</v>
+        <v>0.08406980371917756</v>
       </c>
       <c r="EU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.04727960417496217</v>
+        <v>-0.1103333561902732</v>
       </c>
       <c r="EZ20" t="n">
         <v>-0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.01963905948037998</v>
+        <v>0.02477715930917338</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.006506999670533001</v>
+        <v>0.00569163124628621</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.03376111485827422</v>
+        <v>0.03387049482064364</v>
       </c>
       <c r="FD20" t="n">
         <v>0</v>
       </c>
       <c r="FE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
         <v>0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.04241331494919174</v>
+        <v>-0.03161090551720583</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.04604075009935117</v>
+        <v>0.02660974566238144</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.004987403257038624</v>
+        <v>0.003669325687421027</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.009311224950646341</v>
+        <v>0.02849530536505119</v>
       </c>
       <c r="FM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.009796780033822965</v>
+        <v>-0.09209095522433439</v>
       </c>
       <c r="FR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.003740319932854194</v>
+        <v>0.1832580734887737</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.002628945037036377</v>
+        <v>-0.01157939304630728</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0.00118754240106085</v>
+        <v>0.1169182719667938</v>
       </c>
       <c r="FV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW20" t="n">
         <v>-0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.01334767892083837</v>
+        <v>-0.0957026012993525</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
-        <v>-0.03735117513608368</v>
+        <v>-0.06724594899417363</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.0127489125989381</v>
+        <v>0.008288768609014466</v>
       </c>
       <c r="GE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -12382,19 +12382,19 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2014250280682592</v>
+        <v>0.9336435119923314</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.09200631829579886</v>
+        <v>0.1891344581343335</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08062456975761953</v>
+        <v>-0.4634319324225969</v>
       </c>
       <c r="G22" t="n">
         <v>-0</v>
@@ -12409,52 +12409,52 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1169314741976602</v>
+        <v>0.9337867684822142</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.05743087201827</v>
+        <v>-0.1022455774342854</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.04369611145514982</v>
+        <v>-0.2365064978490205</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.02952704333614772</v>
+        <v>0.1867991567780261</v>
       </c>
       <c r="U22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.02979583603851226</v>
+        <v>-0.08914101262550274</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01735652581989239</v>
+        <v>0.06252024759630975</v>
       </c>
       <c r="Y22" t="n">
         <v>-0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" t="n">
         <v>-0</v>
@@ -12463,7 +12463,7 @@
         <v>-0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.03927605968392829</v>
+        <v>0.01696330619912315</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -12472,13 +12472,13 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.02669298569573883</v>
+        <v>-0.3177397874669632</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.007339199732619318</v>
+        <v>-0.08275983957189997</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>-0</v>
@@ -12487,25 +12487,25 @@
         <v>-0</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.03651967162691664</v>
+        <v>0.1967576498169837</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.01201795162506261</v>
+        <v>-0.07322698771022608</v>
       </c>
       <c r="AP22" t="n">
-        <v>-0.04574413505201786</v>
+        <v>-0.278815428178994</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR22" t="n">
         <v>-0</v>
@@ -12514,37 +12514,37 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.1293526490807242</v>
+        <v>0.8106979718471371</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>-0.03257341192550978</v>
+        <v>-0.2897166598462819</v>
       </c>
       <c r="AY22" t="n">
-        <v>-0.03328006498120321</v>
+        <v>-0.2706203243119994</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
         <v>-0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.03575674675821035</v>
+        <v>0.02284675125929471</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -12553,70 +12553,70 @@
         <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>-0.05044775971662414</v>
+        <v>-0.086730941129772</v>
       </c>
       <c r="BH22" t="n">
-        <v>-0.01130037250511988</v>
+        <v>-0.2277943696046512</v>
       </c>
       <c r="BI22" t="n">
         <v>-0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.04839045177212065</v>
+        <v>0.1419268044432695</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP22" t="n">
-        <v>0.03335745530257225</v>
+        <v>0.1794775702816042</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0.02025835431190887</v>
+        <v>0.1446443526131352</v>
       </c>
       <c r="BR22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
         <v>0</v>
       </c>
       <c r="BT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU22" t="n">
         <v>-0</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.08692125659463283</v>
+        <v>0.6286152328161855</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX22" t="n">
         <v>0</v>
       </c>
       <c r="BY22" t="n">
-        <v>-0.02838406756407246</v>
+        <v>-0.06768770401952547</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.003180392820273569</v>
+        <v>-0.1447493564073785</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC22" t="n">
         <v>-0</v>
@@ -12625,7 +12625,7 @@
         <v>-0</v>
       </c>
       <c r="CE22" t="n">
-        <v>-0.03155980377962528</v>
+        <v>-0.2829813931652317</v>
       </c>
       <c r="CF22" t="n">
         <v>0</v>
@@ -12634,64 +12634,64 @@
         <v>-0</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.009172091426206265</v>
+        <v>0.01362375589936514</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.01876338434070613</v>
+        <v>0.152548192445982</v>
       </c>
       <c r="CJ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK22" t="n">
         <v>0</v>
       </c>
       <c r="CL22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM22" t="n">
         <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>-0.002976341298522299</v>
+        <v>-0.4636140672760531</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ22" t="n">
-        <v>-0.02266085058941829</v>
+        <v>0.3291538945744021</v>
       </c>
       <c r="CR22" t="n">
-        <v>-0.03165135832988876</v>
+        <v>0.1960929674672976</v>
       </c>
       <c r="CS22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT22" t="n">
         <v>-0</v>
       </c>
       <c r="CU22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV22" t="n">
         <v>0</v>
       </c>
       <c r="CW22" t="n">
-        <v>-0.02430928672717448</v>
+        <v>-0.2954205202802397</v>
       </c>
       <c r="CX22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY22" t="n">
         <v>0</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0.00650877281200749</v>
+        <v>-0.06372920324723132</v>
       </c>
       <c r="DA22" t="n">
-        <v>0.0298776638715375</v>
+        <v>0.157872271056631</v>
       </c>
       <c r="DB22" t="n">
         <v>0</v>
@@ -12703,22 +12703,22 @@
         <v>0</v>
       </c>
       <c r="DE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.001680684392392846</v>
+        <v>0.01436450894135135</v>
       </c>
       <c r="DG22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.02874136885777884</v>
+        <v>-0.07591485372028431</v>
       </c>
       <c r="DJ22" t="n">
-        <v>-0.001630632569430148</v>
+        <v>0.04902693049617071</v>
       </c>
       <c r="DK22" t="n">
         <v>0</v>
@@ -12727,31 +12727,31 @@
         <v>-0</v>
       </c>
       <c r="DM22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>-0.03208056501992437</v>
+        <v>-0.1863677507135232</v>
       </c>
       <c r="DP22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR22" t="n">
-        <v>0.03122569615192393</v>
+        <v>-0.07239628860875258</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.02934512895559011</v>
+        <v>0.1264332401981515</v>
       </c>
       <c r="DT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV22" t="n">
         <v>-0</v>
@@ -12760,19 +12760,19 @@
         <v>-0</v>
       </c>
       <c r="DX22" t="n">
-        <v>-0.00244316170148128</v>
+        <v>0.126444838025554</v>
       </c>
       <c r="DY22" t="n">
         <v>0</v>
       </c>
       <c r="DZ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA22" t="n">
-        <v>-0.0330359396089983</v>
+        <v>-0.1169385883580768</v>
       </c>
       <c r="EB22" t="n">
-        <v>-0.01776810495189621</v>
+        <v>0.004610686532801153</v>
       </c>
       <c r="EC22" t="n">
         <v>-0</v>
@@ -12784,28 +12784,28 @@
         <v>-0</v>
       </c>
       <c r="EF22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG22" t="n">
-        <v>-0.01651200922167229</v>
+        <v>-0.08808270468082749</v>
       </c>
       <c r="EH22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ22" t="n">
-        <v>0.01804569646023286</v>
+        <v>-0.1918142533988098</v>
       </c>
       <c r="EK22" t="n">
-        <v>0.007079115459603778</v>
+        <v>0.06845124852703949</v>
       </c>
       <c r="EL22" t="n">
         <v>-0</v>
       </c>
       <c r="EM22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN22" t="n">
         <v>-0</v>
@@ -12814,34 +12814,34 @@
         <v>0</v>
       </c>
       <c r="EP22" t="n">
-        <v>-0.009539738808423888</v>
+        <v>-0.1179414742766615</v>
       </c>
       <c r="EQ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES22" t="n">
-        <v>-0.007461725977477414</v>
+        <v>-0.1454742225429806</v>
       </c>
       <c r="ET22" t="n">
-        <v>-0.03341231867210454</v>
+        <v>-0.1355047883538932</v>
       </c>
       <c r="EU22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX22" t="n">
         <v>-0</v>
       </c>
       <c r="EY22" t="n">
-        <v>-0.02148890221554492</v>
+        <v>-0.3047929322790603</v>
       </c>
       <c r="EZ22" t="n">
         <v>0</v>
@@ -12850,13 +12850,13 @@
         <v>-0</v>
       </c>
       <c r="FB22" t="n">
-        <v>0.002581746181322266</v>
+        <v>-0.05915414286968453</v>
       </c>
       <c r="FC22" t="n">
-        <v>0.02802274663835849</v>
+        <v>0.1272354977926765</v>
       </c>
       <c r="FD22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE22" t="n">
         <v>0</v>
@@ -12865,37 +12865,37 @@
         <v>-0</v>
       </c>
       <c r="FG22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH22" t="n">
-        <v>-0.01692005645209731</v>
+        <v>-0.2083517112023294</v>
       </c>
       <c r="FI22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ22" t="n">
         <v>-0</v>
       </c>
       <c r="FK22" t="n">
-        <v>-0.05096335375462051</v>
+        <v>0.1357175060416868</v>
       </c>
       <c r="FL22" t="n">
-        <v>0.01434206327597235</v>
+        <v>0.1327014232268958</v>
       </c>
       <c r="FM22" t="n">
         <v>0</v>
       </c>
       <c r="FN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO22" t="n">
         <v>0</v>
       </c>
       <c r="FP22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ22" t="n">
-        <v>-0.003215376394661621</v>
+        <v>-0.1509295629654764</v>
       </c>
       <c r="FR22" t="n">
         <v>-0</v>
@@ -12904,37 +12904,37 @@
         <v>-0</v>
       </c>
       <c r="FT22" t="n">
-        <v>-0.001729138103803006</v>
+        <v>-0.0008878248848073911</v>
       </c>
       <c r="FU22" t="n">
-        <v>0.01769520306561963</v>
+        <v>-0.05005401664657584</v>
       </c>
       <c r="FV22" t="n">
         <v>-0</v>
       </c>
       <c r="FW22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ22" t="n">
-        <v>-0.02782295327691912</v>
+        <v>-0.1942478836518023</v>
       </c>
       <c r="GA22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD22" t="n">
-        <v>-0.02353871312291389</v>
+        <v>-0.0190101543056874</v>
       </c>
       <c r="GE22" t="n">
         <v>-0</v>
